--- a/PAMF_DIG F2 - monthly2026-07-11.xlsx
+++ b/PAMF_DIG F2 - monthly2026-07-11.xlsx
@@ -5159,7 +5159,7 @@
         <v>0.09</v>
       </c>
       <c r="N65" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>0.09</v>
       </c>
       <c r="N68" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
@@ -8152,7 +8152,7 @@
         <v>0.09</v>
       </c>
       <c r="N106" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O106" t="inlineStr">
         <is>
@@ -17277,7 +17277,7 @@
         <v>0.09</v>
       </c>
       <c r="N231" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O231" t="inlineStr">
         <is>
@@ -17350,7 +17350,7 @@
         <v>0.09</v>
       </c>
       <c r="N232" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O232" t="inlineStr">
         <is>
